--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104530_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104530_W8.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2818</v>
+        <v>3.6232</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5213</v>
+        <v>2.5823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7605</v>
+        <v>1.0409</v>
       </c>
       <c r="G2" t="n">
-        <v>1.769</v>
+        <v>1.7836</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9666</v>
+        <v>0.976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8024</v>
+        <v>0.8076</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5466</v>
+        <v>1.5396</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4719</v>
+        <v>1.4651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2224</v>
+        <v>0.244</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.075</v>
+        <v>0.2462</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1179</v>
+        <v>-0.0468</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0429</v>
+        <v>0.2929</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7894</v>
+        <v>1.1147</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4858</v>
+        <v>-0.7796</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3036</v>
+        <v>1.8943</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2091</v>
+        <v>0.0297</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5556</v>
+        <v>1.4125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3464</v>
+        <v>-1.3828</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0989</v>
+        <v>0.387</v>
       </c>
       <c r="K3" t="n">
-        <v>0.107</v>
+        <v>1.7582</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0081</v>
+        <v>-1.3712</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.308</v>
+        <v>-0.3573</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6626</v>
+        <v>-0.3457</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3546</v>
+        <v>-0.0116</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0381</v>
+        <v>0.6086</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2411</v>
+        <v>-0.1375</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8678</v>
+        <v>0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4141</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2398</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9295</v>
+        <v>-0.0193</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1692</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0296</v>
+        <v>-0.2166</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4024</v>
+        <v>-0.5544</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3728</v>
+        <v>0.3378</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4121</v>
+        <v>0.0697</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7663</v>
+        <v>0.0927</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3542</v>
+        <v>-0.023</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3825</v>
+        <v>-0.2863</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3639</v>
+        <v>-0.6471</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0186</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7319</v>
+        <v>1.109</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3266</v>
+        <v>0.7823</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0585</v>
+        <v>0.3267</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.8603</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.405</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3214</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0696</v>
+        <v>0.4392</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0159</v>
+        <v>-0.3872</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0159</v>
+        <v>-1.3032</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1732</v>
+        <v>-0.5572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1573</v>
+        <v>-0.746</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.2701</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.9588</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.2288</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0159</v>
+        <v>-1.5733</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1732</v>
+        <v>0.4016</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1573</v>
+        <v>-1.9749</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0696</v>
+        <v>0.4447</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0696</v>
+        <v>0.1691</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.2755</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1633</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0251</v>
+        <v>-0.0697</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1883</v>
+        <v>-0.0144</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3086</v>
+        <v>-0.0144</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.1724</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7516</v>
+        <v>0.1579</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9493</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2315</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5908</v>
+        <v>-0.0144</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3923</v>
+        <v>-0.1724</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9831</v>
+        <v>0.1579</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.238</v>
+        <v>-0.0697</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2571</v>
+        <v>-0.0697</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4951</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1945</v>
+        <v>-0.9377</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3529</v>
+        <v>-0.4004</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5473</v>
+        <v>-0.5373</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6375</v>
+        <v>-1.6322</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1022</v>
+        <v>-0.4766</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5353</v>
+        <v>-1.1557</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5772</v>
+        <v>-0.6602</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6518</v>
+        <v>-0.7347</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0603</v>
+        <v>-0.972</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5496</v>
+        <v>0.2581</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6099</v>
+        <v>-1.2301</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7872</v>
+        <v>0.1694</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3157</v>
+        <v>0.2598</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4715</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4783</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.441</v>
+        <v>-1.153</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6979</v>
+        <v>-0.6619</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7431</v>
+        <v>-0.4911</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6354</v>
+        <v>-1.645</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4732</v>
+        <v>-0.1169</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1621</v>
+        <v>-1.528</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6496</v>
+        <v>-0.602</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7242</v>
+        <v>-0.6765</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9858</v>
+        <v>-1.043</v>
       </c>
       <c r="N8" t="n">
-        <v>0.251</v>
+        <v>0.5595</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2368</v>
+        <v>-1.6025</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3254</v>
+        <v>0.8302</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0484</v>
+        <v>0.3271</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.277</v>
+        <v>0.5032</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-1.4764</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7407</v>
+        <v>-2.5057</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9104</v>
+        <v>-3.7538</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1697</v>
+        <v>1.2481</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9976</v>
+        <v>-3.0117</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3575</v>
+        <v>-3.3738</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3599</v>
+        <v>0.3621</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.9582</v>
+        <v>-2.9844</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.5926</v>
+        <v>-3.6175</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0395</v>
+        <v>-0.0273</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>0.323</v>
+        <v>0.5759</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0212</v>
+        <v>0.2111</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3018</v>
+        <v>0.3648</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1293</v>
+        <v>-3.0323</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1099</v>
+        <v>-3.4804</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0193</v>
+        <v>0.4481</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9343</v>
+        <v>-2.9278</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8641</v>
+        <v>0.8754</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7984</v>
+        <v>-3.8032</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8213</v>
+        <v>-1.8403</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2122</v>
+        <v>1.2066</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.0335</v>
+        <v>-3.0469</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.113</v>
+        <v>-1.0876</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6072</v>
+        <v>-0.5111</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.113</v>
+        <v>-0.4533</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4942</v>
+        <v>-0.0578</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.298</v>
+        <v>-3.8732</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1136</v>
+        <v>-3.1722</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1843</v>
+        <v>-0.701</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6694</v>
+        <v>-3.304</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8381</v>
+        <v>-1.7633</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8312</v>
+        <v>-1.5407</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1614</v>
+        <v>-2.261</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6633</v>
+        <v>-2.007</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4981</v>
+        <v>-0.2541</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.508</v>
+        <v>-1.043</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1749</v>
+        <v>0.2437</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3331</v>
+        <v>-1.2866</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5302</v>
+        <v>0.2228</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0212</v>
+        <v>0.0692</v>
       </c>
       <c r="U11" t="n">
-        <v>0.509</v>
+        <v>0.1535</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2437</v>
+        <v>-4.3331</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3861</v>
+        <v>-4.0828</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8576</v>
+        <v>-0.2503</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2905</v>
+        <v>-3.6813</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7604</v>
+        <v>-1.849</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5301</v>
+        <v>-1.8323</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2301</v>
+        <v>-3.195</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9954</v>
+        <v>-1.6902</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2347</v>
+        <v>-1.5048</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0603</v>
+        <v>-0.4863</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2351</v>
+        <v>-0.1588</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2954</v>
+        <v>-0.3275</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1535</v>
+        <v>0.5075</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1825</v>
+        <v>0.0926</v>
       </c>
       <c r="U12" t="n">
-        <v>0.029</v>
+        <v>0.4149</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2534</v>
+        <v>-0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4141</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.985</v>
+        <v>-10.287</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.8319</v>
+        <v>-13.3986</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8472</v>
+        <v>3.1115</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.8997</v>
+        <v>-15.9229</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.584099999999999</v>
+        <v>-5.5997</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.3155</v>
+        <v>-10.3233</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.0581</v>
+        <v>-9.2765</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.0192</v>
+        <v>-5.162100000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0389</v>
+        <v>-4.114699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.8417</v>
+        <v>-6.646500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5648000000000001</v>
+        <v>-0.4376999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.2767</v>
+        <v>-6.208699999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.268400000000001</v>
+        <v>2.2764</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4757</v>
+        <v>12.5197</v>
       </c>
       <c r="S13" t="n">
-        <v>3.417699999999999</v>
+        <v>4.1335</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4841</v>
+        <v>1.2039</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9335</v>
+        <v>2.9293</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7712</v>
+        <v>-0.7738000000000003</v>
       </c>
       <c r="W13" t="n">
-        <v>4.949400000000001</v>
+        <v>4.917599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.720599999999999</v>
+        <v>-5.6915</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.908</v>
+        <v>5.459</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8151</v>
+        <v>2.3704</v>
       </c>
       <c r="F14" t="n">
-        <v>3.093</v>
+        <v>3.0886</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8245</v>
+        <v>4.8153</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4501</v>
+        <v>-1.4558</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2746</v>
+        <v>6.2711</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8535</v>
+        <v>3.8225</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9679</v>
+        <v>-1.9865</v>
       </c>
       <c r="L14" t="n">
-        <v>5.8214</v>
+        <v>5.8089</v>
       </c>
       <c r="M14" t="n">
-        <v>0.971</v>
+        <v>0.9928</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7558</v>
+        <v>-0.1985</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9043</v>
+        <v>-0.3139</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1485</v>
+        <v>0.1154</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7244</v>
+        <v>4.4242</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5989</v>
+        <v>2.4616</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1255</v>
+        <v>1.9625</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0133</v>
+        <v>3.0184</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7286</v>
+        <v>1.7344</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2848</v>
+        <v>1.284</v>
       </c>
       <c r="J15" t="n">
-        <v>1.485</v>
+        <v>1.4677</v>
       </c>
       <c r="K15" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5283</v>
+        <v>1.5507</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8006</v>
+        <v>0.8176</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1282</v>
+        <v>-0.4365</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0212</v>
+        <v>-0.0955</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1494</v>
+        <v>-0.341</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5037</v>
+        <v>4.3122</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0465</v>
+        <v>2.4815</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4572</v>
+        <v>1.8307</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3206</v>
+        <v>2.3133</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6191</v>
+        <v>2.6112</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2985</v>
+        <v>-0.2979</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9277</v>
+        <v>1.8941</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3062</v>
+        <v>2.2818</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3929</v>
+        <v>0.4192</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2706</v>
+        <v>-0.4564</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9739</v>
+        <v>-0.5021</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2967</v>
+        <v>0.0457</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7219</v>
+        <v>0.8088</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2214</v>
+        <v>-0.4832</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9432</v>
+        <v>1.2919</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0368</v>
+        <v>1.0448</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1198</v>
+        <v>0.1179</v>
       </c>
       <c r="I17" t="n">
-        <v>0.917</v>
+        <v>0.927</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2011</v>
+        <v>-0.2205</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3503</v>
+        <v>-0.3695</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2379</v>
+        <v>1.2653</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9255</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9467</v>
+        <v>-0.6383</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="18">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3433</v>
+        <v>0.4395</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1553</v>
+        <v>0.1536</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1881</v>
+        <v>0.2859</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4199</v>
+        <v>0.4221</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2944</v>
+        <v>0.293</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2944</v>
+        <v>0.293</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2338</v>
+        <v>-0.1405</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2279</v>
+        <v>0.3139</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3733</v>
+        <v>-0.2706</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6012</v>
+        <v>0.5845</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7731</v>
+        <v>1.7787</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4457</v>
+        <v>0.4561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3274</v>
+        <v>1.3226</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8848</v>
+        <v>0.8728</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8883</v>
+        <v>0.9058</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1628</v>
+        <v>1.1768</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0008</v>
+        <v>-0.9184</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5139</v>
+        <v>-0.549</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0516</v>
+        <v>0.0861</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.552</v>
+        <v>-2.3069</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5004</v>
+        <v>2.393</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0837</v>
+        <v>1.2173</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0304</v>
+        <v>1.7861</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0533</v>
+        <v>-0.5688</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1347</v>
+        <v>0.2533</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0173</v>
+        <v>1.7582</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.152</v>
+        <v>-1.5048</v>
       </c>
       <c r="M20" t="n">
-        <v>0.051</v>
+        <v>0.9639</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0477</v>
+        <v>0.028</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4216</v>
+        <v>-0.5574</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>-0.5508</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0042</v>
+        <v>-0.0066</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5638</v>
+        <v>0.0766</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5712</v>
+        <v>-0.5576</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0074</v>
+        <v>0.6342</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8785</v>
+        <v>-0.0813</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7879</v>
+        <v>-0.0261</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0906</v>
+        <v>-0.0552</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1711</v>
+        <v>-0.1394</v>
       </c>
       <c r="K21" t="n">
-        <v>1.475</v>
+        <v>0.0172</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3039</v>
+        <v>-0.1566</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7074</v>
+        <v>0.0581</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3129</v>
+        <v>-0.0433</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3946</v>
+        <v>0.1014</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1228</v>
+        <v>-0.2973</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.113</v>
+        <v>-0.4182</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9902</v>
+        <v>0.1209</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5757</v>
+        <v>-0.4129</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6245</v>
+        <v>-0.0239</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0488</v>
+        <v>-0.3889</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2075</v>
+        <v>1.8762</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7805</v>
+        <v>1.7838</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5731000000000001</v>
+        <v>0.0924</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2682</v>
+        <v>1.1412</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7663</v>
+        <v>1.4544</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4981</v>
+        <v>-0.3132</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9392</v>
+        <v>0.7351</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0142</v>
+        <v>0.3294</v>
       </c>
       <c r="O22" t="n">
-        <v>0.925</v>
+        <v>0.4057</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8147</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2219</v>
+        <v>0.028</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9043</v>
+        <v>-0.523</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3176</v>
+        <v>0.551</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2534</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4141</v>
+        <v>1.6342</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7574</v>
+        <v>-2.2047</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8731</v>
+        <v>-3.8362</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1157</v>
+        <v>1.6314</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3459</v>
+        <v>-1.3454</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5352</v>
+        <v>-1.5392</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1893</v>
+        <v>0.1939</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.621</v>
+        <v>-1.6339</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7703</v>
+        <v>-1.7829</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2751</v>
+        <v>0.2886</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1764</v>
+        <v>0.7341</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0162</v>
+        <v>0.0741</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1602</v>
+        <v>0.66</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4958</v>
+        <v>-2.3184</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2474</v>
+        <v>-3.1001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7516</v>
+        <v>0.7817</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6978</v>
+        <v>0.7057</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3018</v>
+        <v>-0.2907</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9964</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0864</v>
+        <v>-1.1044</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7842</v>
+        <v>1.8101</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1151</v>
+        <v>1.1335</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4869</v>
+        <v>-0.3412</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9467</v>
+        <v>0.1228</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4597</v>
+        <v>-0.464</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.9849</v>
+        <v>10.9843</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8471</v>
+        <v>-3.1114</v>
       </c>
       <c r="F25" t="n">
-        <v>13.8321</v>
+        <v>14.0955</v>
       </c>
       <c r="G25" t="n">
-        <v>15.8996</v>
+        <v>15.923</v>
       </c>
       <c r="H25" t="n">
-        <v>5.584000000000001</v>
+        <v>5.5998</v>
       </c>
       <c r="I25" t="n">
-        <v>10.3156</v>
+        <v>10.3234</v>
       </c>
       <c r="J25" t="n">
-        <v>6.841499999999999</v>
+        <v>6.646399999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5647000000000004</v>
+        <v>0.4376000000000004</v>
       </c>
       <c r="L25" t="n">
-        <v>6.2767</v>
+        <v>6.2086</v>
       </c>
       <c r="M25" t="n">
-        <v>9.0581</v>
+        <v>9.2766</v>
       </c>
       <c r="N25" t="n">
-        <v>5.0193</v>
+        <v>5.162</v>
       </c>
       <c r="O25" t="n">
-        <v>4.0388</v>
+        <v>4.1146</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4177</v>
+        <v>-3.4364</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.9336</v>
+        <v>-2.9295</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.484</v>
+        <v>-0.5069999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7713000000000003</v>
+        <v>0.774</v>
       </c>
       <c r="W25" t="n">
-        <v>5.720700000000001</v>
+        <v>5.691599999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.9494</v>
+        <v>-4.9175</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104530_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104530_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.6915</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104530_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.9175</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
